--- a/Archived_HE_Data/hedata_2026-08-11.xlsx
+++ b/Archived_HE_Data/hedata_2026-08-11.xlsx
@@ -697,6 +697,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5952</t>
   </si>
   <si>
+    <t>Workforce Development and Community Education Office Assistant (Part Time Benefited)</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/6007</t>
+  </si>
+  <si>
     <t>Instructor/Assistant Professor of Powerline Technology</t>
   </si>
   <si>
@@ -706,15 +715,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5859</t>
   </si>
   <si>
-    <t>Workforce Development and Community Education Office Assistant (Part Time Benefited)</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/6007</t>
-  </si>
-  <si>
     <t>Physics Student Worker (lab) (S. Schutten)</t>
   </si>
   <si>
@@ -733,6 +733,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5876</t>
   </si>
   <si>
+    <t>Instructor/Assistant Professor of Information Systems</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5974</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Industrial Safety</t>
   </si>
   <si>
@@ -742,15 +751,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5258</t>
   </si>
   <si>
-    <t>Instructor/Assistant Professor of Information Systems</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5974</t>
-  </si>
-  <si>
     <t>Adjunct Faculty - Physics</t>
   </si>
   <si>
@@ -784,6 +784,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5918</t>
   </si>
   <si>
+    <t>Adjunct Faculty - Certified Nursing Assistant (CNA) (Rock Springs &amp; Evanston)</t>
+  </si>
+  <si>
+    <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5503</t>
+  </si>
+  <si>
     <t>IT Support Technician</t>
   </si>
   <si>
@@ -793,15 +802,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5984</t>
   </si>
   <si>
-    <t>Adjunct Faculty - Certified Nursing Assistant (CNA) (Rock Springs &amp; Evanston)</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5503</t>
-  </si>
-  <si>
     <t>Adjunct Faculty - Business</t>
   </si>
   <si>
@@ -811,6 +811,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5933</t>
   </si>
   <si>
+    <t>Adjunct Faculty- Physical or Outdoor Activity</t>
+  </si>
+  <si>
+    <t>2025-06-17</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5601</t>
+  </si>
+  <si>
     <t>Children's Center Part-Time Aide (Substitute)</t>
   </si>
   <si>
@@ -820,15 +829,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5990</t>
   </si>
   <si>
-    <t>Adjunct Faculty- Physical or Outdoor Activity</t>
-  </si>
-  <si>
-    <t>2025-06-17</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5601</t>
-  </si>
-  <si>
     <t>Instructor/Assistant Professor of Electrical &amp; Instrumentation (Rock Springs Campus)</t>
   </si>
   <si>
@@ -838,6 +838,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5940</t>
   </si>
   <si>
+    <t>Bus Drivers - Part Time</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5718</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Nutrition</t>
   </si>
   <si>
@@ -847,15 +856,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5995</t>
   </si>
   <si>
-    <t>Bus Drivers - Part Time</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5718</t>
-  </si>
-  <si>
     <t>Multimedia Student Worker (Fall 2026)</t>
   </si>
   <si>
@@ -865,6 +865,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5946</t>
   </si>
   <si>
+    <t>Adjunct Faculty - Biology</t>
+  </si>
+  <si>
+    <t>2025-12-11</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5805</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Medical Term</t>
   </si>
   <si>
@@ -874,21 +883,21 @@
     <t>https://wwcwy.peopleadmin.com/postings/5999</t>
   </si>
   <si>
-    <t>Adjunct Faculty - Biology</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5805</t>
-  </si>
-  <si>
     <t>MAVERICK The Mascot Student Worker (Fall 2026)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5950</t>
   </si>
   <si>
+    <t>Director of Workforce Development and the Green River Center</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5818</t>
+  </si>
+  <si>
     <t>Student Library Aide</t>
   </si>
   <si>
@@ -898,15 +907,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/6005</t>
   </si>
   <si>
-    <t>Director of Workforce Development and the Green River Center</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5818</t>
-  </si>
-  <si>
     <t>Fitness Center - Student Worker</t>
   </si>
   <si>
@@ -937,21 +937,21 @@
     <t>https://wwcwy.peopleadmin.com/postings/5877</t>
   </si>
   <si>
+    <t>Musical Theatre Director (Seasonal Assignment)</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5976</t>
+  </si>
+  <si>
     <t>Adjunct Faculty-Commerical Driver's License (CDL)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5262</t>
   </si>
   <si>
-    <t>Musical Theatre Director (Seasonal Assignment)</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5976</t>
-  </si>
-  <si>
     <t>Workforce MSHA Instructor</t>
   </si>
   <si>
@@ -985,6 +985,15 @@
     <t>https://wwcwy.peopleadmin.com/postings/5926</t>
   </si>
   <si>
+    <t>Instructor/Assistant Professor of Industrial Maintenance</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5552</t>
+  </si>
+  <si>
     <t>Systems Administrator</t>
   </si>
   <si>
@@ -994,15 +1003,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/5986</t>
   </si>
   <si>
-    <t>Instructor/Assistant Professor of Industrial Maintenance</t>
-  </si>
-  <si>
-    <t>2025-04-18</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5552</t>
-  </si>
-  <si>
     <t>Adjunct Faculty - Geology</t>
   </si>
   <si>
@@ -1012,6 +1012,12 @@
     <t>https://wwcwy.peopleadmin.com/postings/5938</t>
   </si>
   <si>
+    <t>INBRE Research Technicians</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5716</t>
+  </si>
+  <si>
     <t>Accounting Technician</t>
   </si>
   <si>
@@ -1021,36 +1027,39 @@
     <t>https://wwcwy.peopleadmin.com/postings/5991</t>
   </si>
   <si>
-    <t>INBRE Research Technicians</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5716</t>
-  </si>
-  <si>
     <t>Print Shop Student Worker (Fall 2026)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5944</t>
   </si>
   <si>
+    <t>Lifeguard 2025-2026</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5719</t>
+  </si>
+  <si>
     <t>Adjunct Faculty - Information Systems</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5997</t>
   </si>
   <si>
-    <t>Lifeguard 2025-2026</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5719</t>
-  </si>
-  <si>
     <t>President's Social Media Student Worker (Fall 2026)</t>
   </si>
   <si>
     <t>https://wwcwy.peopleadmin.com/postings/5948</t>
   </si>
   <si>
+    <t>Adjunct Faculty - History</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>https://wwcwy.peopleadmin.com/postings/5809</t>
+  </si>
+  <si>
     <t>Admissions Counselor</t>
   </si>
   <si>
@@ -1060,15 +1069,6 @@
     <t>https://wwcwy.peopleadmin.com/postings/6003</t>
   </si>
   <si>
-    <t>Adjunct Faculty - History</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>https://wwcwy.peopleadmin.com/postings/5809</t>
-  </si>
-  <si>
     <t>Adjunct</t>
   </si>
   <si>
@@ -1429,6 +1429,12 @@
     <t>https://jobs.sheridan.edu/postings/4511</t>
   </si>
   <si>
+    <t>Part-time Faculty Pool - Composites Manufacturing</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/4097</t>
+  </si>
+  <si>
     <t>Hospitality Faculty Coordinator</t>
   </si>
   <si>
@@ -1438,12 +1444,6 @@
     <t>https://jobs.sheridan.edu/postings/4660</t>
   </si>
   <si>
-    <t>Part-time Faculty Pool - Composites Manufacturing</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/4097</t>
-  </si>
-  <si>
     <t>Part-time Academic Support Services Pool- Academic Support Tutor</t>
   </si>
   <si>
@@ -1519,6 +1519,12 @@
     <t>https://jobs.sheridan.edu/postings/4684</t>
   </si>
   <si>
+    <t>(Student Position) Box Office Assistant</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/4560</t>
+  </si>
+  <si>
     <t>Part-time Faculty Pool - Community Interest (CI) Johnson County</t>
   </si>
   <si>
@@ -1528,12 +1534,6 @@
     <t>https://jobs.sheridan.edu/postings/4084</t>
   </si>
   <si>
-    <t>(Student Position) Box Office Assistant</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/4560</t>
-  </si>
-  <si>
     <t>Part-time Faculty Pool - Electrical Apprenticeship Instructor</t>
   </si>
   <si>
@@ -1636,18 +1636,18 @@
     <t>https://jobs.sheridan.edu/postings/4092</t>
   </si>
   <si>
+    <t>Part-time Faculty Pool - Accounting Instructor</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/3763</t>
+  </si>
+  <si>
     <t>(Student Position) Enrollment Services Assistant</t>
   </si>
   <si>
     <t>https://jobs.sheridan.edu/postings/4500</t>
   </si>
   <si>
-    <t>Part-time Faculty Pool - Accounting Instructor</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/3763</t>
-  </si>
-  <si>
     <t>(Student Position) Sports &amp; Recreation Manager</t>
   </si>
   <si>
@@ -1744,6 +1744,12 @@
     <t>https://jobs.sheridan.edu/postings/4681</t>
   </si>
   <si>
+    <t>(Student Position) Peer Tutor</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/4523</t>
+  </si>
+  <si>
     <t>Part-time Faculty Pool - Massage Therapy Instructor</t>
   </si>
   <si>
@@ -1753,12 +1759,6 @@
     <t>https://jobs.sheridan.edu/postings/4048</t>
   </si>
   <si>
-    <t>(Student Position) Peer Tutor</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/4523</t>
-  </si>
-  <si>
     <t>Part-time Faculty Pool - Engineering Science and Engineering Tech Instructor</t>
   </si>
   <si>
@@ -1858,18 +1858,18 @@
     <t>https://jobs.sheridan.edu/postings/4089</t>
   </si>
   <si>
+    <t>Part-time Faculty Pool - Business Instructor</t>
+  </si>
+  <si>
+    <t>https://jobs.sheridan.edu/postings/3760</t>
+  </si>
+  <si>
     <t>(Student Position) Dental Hygiene Program Assistant</t>
   </si>
   <si>
     <t>https://jobs.sheridan.edu/postings/4497</t>
   </si>
   <si>
-    <t>Part-time Faculty Pool - Business Instructor</t>
-  </si>
-  <si>
-    <t>https://jobs.sheridan.edu/postings/3760</t>
-  </si>
-  <si>
     <t>(Student Position) Sports and Recreation Assistant</t>
   </si>
   <si>
@@ -1954,18 +1954,24 @@
     <t>https://northwestcollege.simplehire.com/postings/2693</t>
   </si>
   <si>
+    <t>Engineer, Senior - Facilities Engineering</t>
+  </si>
+  <si>
+    <t>Laramie, WY, United States</t>
+  </si>
+  <si>
+    <t>University of Wyoming</t>
+  </si>
+  <si>
+    <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261770</t>
+  </si>
+  <si>
     <t>Hourly Pooled - Research Assistant, Ecosystem Science &amp; Management</t>
   </si>
   <si>
-    <t>Laramie, WY, United States</t>
-  </si>
-  <si>
     <t>2026-08-10</t>
   </si>
   <si>
-    <t>University of Wyoming</t>
-  </si>
-  <si>
     <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262095</t>
   </si>
   <si>
@@ -2117,12 +2123,6 @@
   </si>
   <si>
     <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-  </si>
-  <si>
-    <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-  </si>
-  <si>
-    <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
   </si>
 </sst>
 </file>
@@ -5103,13 +5103,13 @@
         <v>223</v>
       </c>
       <c r="C132" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="D132" t="s">
         <v>225</v>
       </c>
       <c r="E132" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F132" s="1">
         <v>46245</v>
@@ -5117,13 +5117,13 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B133" t="s">
         <v>223</v>
       </c>
       <c r="C133" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="D133" t="s">
         <v>225</v>
@@ -5163,7 +5163,7 @@
         <v>223</v>
       </c>
       <c r="C135" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D135" t="s">
         <v>225</v>
@@ -5283,13 +5283,13 @@
         <v>223</v>
       </c>
       <c r="C141" t="s">
-        <v>333</v>
+        <v>275</v>
       </c>
       <c r="D141" t="s">
         <v>225</v>
       </c>
       <c r="E141" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F141" s="1">
         <v>46245</v>
@@ -5297,13 +5297,13 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B142" t="s">
         <v>223</v>
       </c>
       <c r="C142" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="D142" t="s">
         <v>225</v>
@@ -5343,7 +5343,7 @@
         <v>223</v>
       </c>
       <c r="C144" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
         <v>225</v>
@@ -5363,7 +5363,7 @@
         <v>223</v>
       </c>
       <c r="C145" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D145" t="s">
         <v>225</v>
@@ -5763,7 +5763,7 @@
         <v>382</v>
       </c>
       <c r="C165" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D165" t="s">
         <v>384</v>
@@ -6443,13 +6443,13 @@
         <v>458</v>
       </c>
       <c r="C199" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D199" t="s">
         <v>460</v>
       </c>
       <c r="E199" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F199" s="1">
         <v>46245</v>
@@ -6457,13 +6457,13 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B200" t="s">
         <v>458</v>
       </c>
       <c r="C200" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="D200" t="s">
         <v>460</v>
@@ -6683,13 +6683,13 @@
         <v>458</v>
       </c>
       <c r="C211" t="s">
-        <v>502</v>
+        <v>234</v>
       </c>
       <c r="D211" t="s">
         <v>460</v>
       </c>
       <c r="E211" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F211" s="1">
         <v>46245</v>
@@ -6697,13 +6697,13 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B212" t="s">
         <v>458</v>
       </c>
       <c r="C212" t="s">
-        <v>234</v>
+        <v>504</v>
       </c>
       <c r="D212" t="s">
         <v>460</v>
@@ -6883,7 +6883,7 @@
         <v>458</v>
       </c>
       <c r="C221" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D221" t="s">
         <v>460</v>
@@ -6923,7 +6923,7 @@
         <v>458</v>
       </c>
       <c r="C223" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D223" t="s">
         <v>460</v>
@@ -6963,7 +6963,7 @@
         <v>458</v>
       </c>
       <c r="C225" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D225" t="s">
         <v>460</v>
@@ -7003,7 +7003,7 @@
         <v>458</v>
       </c>
       <c r="C227" t="s">
-        <v>469</v>
+        <v>534</v>
       </c>
       <c r="D227" t="s">
         <v>460</v>
@@ -7023,7 +7023,7 @@
         <v>458</v>
       </c>
       <c r="C228" t="s">
-        <v>534</v>
+        <v>469</v>
       </c>
       <c r="D228" t="s">
         <v>460</v>
@@ -7223,7 +7223,7 @@
         <v>458</v>
       </c>
       <c r="C238" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D238" t="s">
         <v>460</v>
@@ -7343,13 +7343,13 @@
         <v>458</v>
       </c>
       <c r="C244" t="s">
-        <v>577</v>
+        <v>492</v>
       </c>
       <c r="D244" t="s">
         <v>460</v>
       </c>
       <c r="E244" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F244" s="1">
         <v>46245</v>
@@ -7357,13 +7357,13 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B245" t="s">
         <v>458</v>
       </c>
       <c r="C245" t="s">
-        <v>492</v>
+        <v>579</v>
       </c>
       <c r="D245" t="s">
         <v>460</v>
@@ -7423,7 +7423,7 @@
         <v>458</v>
       </c>
       <c r="C248" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D248" t="s">
         <v>460</v>
@@ -7623,7 +7623,7 @@
         <v>458</v>
       </c>
       <c r="C258" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D258" t="s">
         <v>460</v>
@@ -7663,7 +7663,7 @@
         <v>458</v>
       </c>
       <c r="C260" t="s">
-        <v>469</v>
+        <v>534</v>
       </c>
       <c r="D260" t="s">
         <v>460</v>
@@ -7683,7 +7683,7 @@
         <v>458</v>
       </c>
       <c r="C261" t="s">
-        <v>534</v>
+        <v>469</v>
       </c>
       <c r="D261" t="s">
         <v>460</v>
@@ -7703,7 +7703,7 @@
         <v>458</v>
       </c>
       <c r="C262" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D262" t="s">
         <v>460</v>
@@ -7803,7 +7803,7 @@
         <v>628</v>
       </c>
       <c r="C267" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D267" t="s">
         <v>630</v>
@@ -7863,7 +7863,7 @@
         <v>628</v>
       </c>
       <c r="C270" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D270" t="s">
         <v>630</v>
@@ -7883,7 +7883,7 @@
         <v>628</v>
       </c>
       <c r="C271" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D271" t="s">
         <v>630</v>
@@ -7903,7 +7903,7 @@
         <v>628</v>
       </c>
       <c r="C272" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D272" t="s">
         <v>630</v>
@@ -7923,13 +7923,13 @@
         <v>647</v>
       </c>
       <c r="C273" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D273" t="s">
+        <v>648</v>
+      </c>
+      <c r="E273" t="s">
         <v>649</v>
-      </c>
-      <c r="E273" t="s">
-        <v>650</v>
       </c>
       <c r="F273" s="1">
         <v>46245</v>
@@ -7937,16 +7937,16 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
+        <v>650</v>
+      </c>
+      <c r="B274" t="s">
+        <v>647</v>
+      </c>
+      <c r="C274" t="s">
         <v>651</v>
       </c>
-      <c r="B274" t="s">
-        <v>647</v>
-      </c>
-      <c r="C274" t="s">
-        <v>648</v>
-      </c>
       <c r="D274" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E274" t="s">
         <v>652</v>
@@ -7963,10 +7963,10 @@
         <v>647</v>
       </c>
       <c r="C275" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D275" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E275" t="s">
         <v>654</v>
@@ -7983,10 +7983,10 @@
         <v>647</v>
       </c>
       <c r="C276" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D276" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E276" t="s">
         <v>656</v>
@@ -8003,10 +8003,10 @@
         <v>647</v>
       </c>
       <c r="C277" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D277" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E277" t="s">
         <v>658</v>
@@ -8023,13 +8023,13 @@
         <v>647</v>
       </c>
       <c r="C278" t="s">
+        <v>651</v>
+      </c>
+      <c r="D278" t="s">
+        <v>648</v>
+      </c>
+      <c r="E278" t="s">
         <v>660</v>
-      </c>
-      <c r="D278" t="s">
-        <v>649</v>
-      </c>
-      <c r="E278" t="s">
-        <v>661</v>
       </c>
       <c r="F278" s="1">
         <v>46245</v>
@@ -8037,16 +8037,16 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
+        <v>661</v>
+      </c>
+      <c r="B279" t="s">
+        <v>647</v>
+      </c>
+      <c r="C279" t="s">
         <v>662</v>
       </c>
-      <c r="B279" t="s">
-        <v>647</v>
-      </c>
-      <c r="C279" t="s">
-        <v>383</v>
-      </c>
       <c r="D279" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E279" t="s">
         <v>663</v>
@@ -8063,10 +8063,10 @@
         <v>647</v>
       </c>
       <c r="C280" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D280" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E280" t="s">
         <v>665</v>
@@ -8083,10 +8083,10 @@
         <v>647</v>
       </c>
       <c r="C281" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D281" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E281" t="s">
         <v>667</v>
@@ -8103,10 +8103,10 @@
         <v>647</v>
       </c>
       <c r="C282" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D282" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E282" t="s">
         <v>669</v>
@@ -8123,10 +8123,10 @@
         <v>647</v>
       </c>
       <c r="C283" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D283" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E283" t="s">
         <v>671</v>
@@ -8143,10 +8143,10 @@
         <v>647</v>
       </c>
       <c r="C284" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D284" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E284" t="s">
         <v>673</v>
@@ -8166,7 +8166,7 @@
         <v>513</v>
       </c>
       <c r="D285" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E285" t="s">
         <v>675</v>
@@ -8183,10 +8183,10 @@
         <v>647</v>
       </c>
       <c r="C286" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D286" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E286" t="s">
         <v>677</v>
@@ -8203,13 +8203,13 @@
         <v>647</v>
       </c>
       <c r="C287" t="s">
+        <v>662</v>
+      </c>
+      <c r="D287" t="s">
+        <v>648</v>
+      </c>
+      <c r="E287" t="s">
         <v>679</v>
-      </c>
-      <c r="D287" t="s">
-        <v>649</v>
-      </c>
-      <c r="E287" t="s">
-        <v>680</v>
       </c>
       <c r="F287" s="1">
         <v>46245</v>
@@ -8217,19 +8217,19 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
+        <v>680</v>
+      </c>
+      <c r="B288" t="s">
+        <v>647</v>
+      </c>
+      <c r="C288" t="s">
         <v>681</v>
       </c>
-      <c r="B288" t="s">
+      <c r="D288" t="s">
+        <v>648</v>
+      </c>
+      <c r="E288" t="s">
         <v>682</v>
-      </c>
-      <c r="C288" t="s">
-        <v>683</v>
-      </c>
-      <c r="D288" t="s">
-        <v>649</v>
-      </c>
-      <c r="E288" t="s">
-        <v>684</v>
       </c>
       <c r="F288" s="1">
         <v>46245</v>
@@ -8237,16 +8237,16 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
+        <v>683</v>
+      </c>
+      <c r="B289" t="s">
+        <v>684</v>
+      </c>
+      <c r="C289" t="s">
         <v>685</v>
       </c>
-      <c r="B289" t="s">
-        <v>647</v>
-      </c>
-      <c r="C289" t="s">
-        <v>683</v>
-      </c>
       <c r="D289" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E289" t="s">
         <v>686</v>
@@ -8263,10 +8263,10 @@
         <v>647</v>
       </c>
       <c r="C290" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D290" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E290" t="s">
         <v>688</v>
@@ -8283,10 +8283,10 @@
         <v>647</v>
       </c>
       <c r="C291" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D291" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E291" t="s">
         <v>690</v>
@@ -8303,10 +8303,10 @@
         <v>647</v>
       </c>
       <c r="C292" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D292" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E292" t="s">
         <v>692</v>
@@ -8323,10 +8323,10 @@
         <v>647</v>
       </c>
       <c r="C293" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D293" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E293" t="s">
         <v>694</v>
@@ -8343,10 +8343,10 @@
         <v>647</v>
       </c>
       <c r="C294" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D294" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E294" t="s">
         <v>696</v>
@@ -8363,10 +8363,10 @@
         <v>647</v>
       </c>
       <c r="C295" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D295" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E295" t="s">
         <v>698</v>
@@ -8383,10 +8383,10 @@
         <v>647</v>
       </c>
       <c r="C296" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D296" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E296" t="s">
         <v>700</v>
@@ -8403,10 +8403,10 @@
         <v>647</v>
       </c>
       <c r="C297" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D297" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E297" t="s">
         <v>702</v>
@@ -8423,13 +8423,13 @@
         <v>647</v>
       </c>
       <c r="C298" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D298" t="s">
+        <v>648</v>
+      </c>
+      <c r="E298" t="s">
         <v>649</v>
-      </c>
-      <c r="E298" t="s">
-        <v>650</v>
       </c>
       <c r="F298" s="1">
         <v>46245</v>
@@ -8437,16 +8437,16 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
+        <v>650</v>
+      </c>
+      <c r="B299" t="s">
+        <v>647</v>
+      </c>
+      <c r="C299" t="s">
         <v>651</v>
       </c>
-      <c r="B299" t="s">
-        <v>647</v>
-      </c>
-      <c r="C299" t="s">
-        <v>648</v>
-      </c>
       <c r="D299" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E299" t="s">
         <v>652</v>
@@ -8463,10 +8463,10 @@
         <v>647</v>
       </c>
       <c r="C300" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D300" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E300" t="s">
         <v>654</v>
@@ -8483,10 +8483,10 @@
         <v>647</v>
       </c>
       <c r="C301" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D301" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E301" t="s">
         <v>656</v>
@@ -8503,10 +8503,10 @@
         <v>647</v>
       </c>
       <c r="C302" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D302" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E302" t="s">
         <v>658</v>
@@ -8523,13 +8523,13 @@
         <v>647</v>
       </c>
       <c r="C303" t="s">
+        <v>651</v>
+      </c>
+      <c r="D303" t="s">
+        <v>648</v>
+      </c>
+      <c r="E303" t="s">
         <v>660</v>
-      </c>
-      <c r="D303" t="s">
-        <v>649</v>
-      </c>
-      <c r="E303" t="s">
-        <v>661</v>
       </c>
       <c r="F303" s="1">
         <v>46245</v>
@@ -8537,16 +8537,16 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
+        <v>661</v>
+      </c>
+      <c r="B304" t="s">
+        <v>647</v>
+      </c>
+      <c r="C304" t="s">
         <v>662</v>
       </c>
-      <c r="B304" t="s">
-        <v>647</v>
-      </c>
-      <c r="C304" t="s">
-        <v>383</v>
-      </c>
       <c r="D304" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E304" t="s">
         <v>663</v>
@@ -8563,10 +8563,10 @@
         <v>647</v>
       </c>
       <c r="C305" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D305" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E305" t="s">
         <v>665</v>
@@ -8583,10 +8583,10 @@
         <v>647</v>
       </c>
       <c r="C306" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D306" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E306" t="s">
         <v>667</v>
@@ -8603,10 +8603,10 @@
         <v>647</v>
       </c>
       <c r="C307" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D307" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E307" t="s">
         <v>669</v>
@@ -8623,10 +8623,10 @@
         <v>647</v>
       </c>
       <c r="C308" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D308" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E308" t="s">
         <v>671</v>
@@ -8643,10 +8643,10 @@
         <v>647</v>
       </c>
       <c r="C309" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D309" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E309" t="s">
         <v>673</v>
@@ -8666,7 +8666,7 @@
         <v>513</v>
       </c>
       <c r="D310" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E310" t="s">
         <v>675</v>
@@ -8683,10 +8683,10 @@
         <v>647</v>
       </c>
       <c r="C311" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D311" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E311" t="s">
         <v>677</v>
@@ -8703,13 +8703,13 @@
         <v>647</v>
       </c>
       <c r="C312" t="s">
+        <v>662</v>
+      </c>
+      <c r="D312" t="s">
+        <v>648</v>
+      </c>
+      <c r="E312" t="s">
         <v>679</v>
-      </c>
-      <c r="D312" t="s">
-        <v>649</v>
-      </c>
-      <c r="E312" t="s">
-        <v>680</v>
       </c>
       <c r="F312" s="1">
         <v>46245</v>
@@ -8717,19 +8717,19 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
+        <v>680</v>
+      </c>
+      <c r="B313" t="s">
+        <v>647</v>
+      </c>
+      <c r="C313" t="s">
         <v>681</v>
       </c>
-      <c r="B313" t="s">
+      <c r="D313" t="s">
+        <v>648</v>
+      </c>
+      <c r="E313" t="s">
         <v>682</v>
-      </c>
-      <c r="C313" t="s">
-        <v>683</v>
-      </c>
-      <c r="D313" t="s">
-        <v>649</v>
-      </c>
-      <c r="E313" t="s">
-        <v>684</v>
       </c>
       <c r="F313" s="1">
         <v>46245</v>
@@ -8737,16 +8737,16 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
+        <v>683</v>
+      </c>
+      <c r="B314" t="s">
+        <v>684</v>
+      </c>
+      <c r="C314" t="s">
         <v>685</v>
       </c>
-      <c r="B314" t="s">
-        <v>647</v>
-      </c>
-      <c r="C314" t="s">
-        <v>683</v>
-      </c>
       <c r="D314" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E314" t="s">
         <v>686</v>
@@ -8763,10 +8763,10 @@
         <v>647</v>
       </c>
       <c r="C315" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D315" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E315" t="s">
         <v>688</v>
@@ -8783,10 +8783,10 @@
         <v>647</v>
       </c>
       <c r="C316" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D316" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E316" t="s">
         <v>690</v>
@@ -8803,10 +8803,10 @@
         <v>647</v>
       </c>
       <c r="C317" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D317" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E317" t="s">
         <v>692</v>
@@ -8823,10 +8823,10 @@
         <v>647</v>
       </c>
       <c r="C318" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D318" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E318" t="s">
         <v>694</v>
@@ -8843,10 +8843,10 @@
         <v>647</v>
       </c>
       <c r="C319" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D319" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E319" t="s">
         <v>696</v>
@@ -8863,10 +8863,10 @@
         <v>647</v>
       </c>
       <c r="C320" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D320" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E320" t="s">
         <v>698</v>
@@ -8883,10 +8883,10 @@
         <v>647</v>
       </c>
       <c r="C321" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D321" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E321" t="s">
         <v>700</v>
@@ -8903,10 +8903,10 @@
         <v>647</v>
       </c>
       <c r="C322" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D322" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E322" t="s">
         <v>702</v>
@@ -8923,13 +8923,13 @@
         <v>647</v>
       </c>
       <c r="C323" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D323" t="s">
+        <v>648</v>
+      </c>
+      <c r="E323" t="s">
         <v>649</v>
-      </c>
-      <c r="E323" t="s">
-        <v>650</v>
       </c>
       <c r="F323" s="1">
         <v>46245</v>
@@ -8937,16 +8937,16 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
+        <v>650</v>
+      </c>
+      <c r="B324" t="s">
+        <v>647</v>
+      </c>
+      <c r="C324" t="s">
         <v>651</v>
       </c>
-      <c r="B324" t="s">
-        <v>647</v>
-      </c>
-      <c r="C324" t="s">
-        <v>648</v>
-      </c>
       <c r="D324" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E324" t="s">
         <v>652</v>
@@ -8963,10 +8963,10 @@
         <v>647</v>
       </c>
       <c r="C325" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D325" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E325" t="s">
         <v>654</v>
@@ -8983,10 +8983,10 @@
         <v>647</v>
       </c>
       <c r="C326" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D326" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E326" t="s">
         <v>656</v>
@@ -9003,10 +9003,10 @@
         <v>647</v>
       </c>
       <c r="C327" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D327" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E327" t="s">
         <v>658</v>
@@ -9023,13 +9023,13 @@
         <v>647</v>
       </c>
       <c r="C328" t="s">
+        <v>651</v>
+      </c>
+      <c r="D328" t="s">
+        <v>648</v>
+      </c>
+      <c r="E328" t="s">
         <v>660</v>
-      </c>
-      <c r="D328" t="s">
-        <v>649</v>
-      </c>
-      <c r="E328" t="s">
-        <v>661</v>
       </c>
       <c r="F328" s="1">
         <v>46245</v>
@@ -9037,16 +9037,16 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
+        <v>661</v>
+      </c>
+      <c r="B329" t="s">
+        <v>647</v>
+      </c>
+      <c r="C329" t="s">
         <v>662</v>
       </c>
-      <c r="B329" t="s">
-        <v>647</v>
-      </c>
-      <c r="C329" t="s">
-        <v>383</v>
-      </c>
       <c r="D329" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E329" t="s">
         <v>663</v>
@@ -9063,10 +9063,10 @@
         <v>647</v>
       </c>
       <c r="C330" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D330" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E330" t="s">
         <v>665</v>
@@ -9083,10 +9083,10 @@
         <v>647</v>
       </c>
       <c r="C331" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D331" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E331" t="s">
         <v>667</v>
@@ -9103,10 +9103,10 @@
         <v>647</v>
       </c>
       <c r="C332" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D332" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E332" t="s">
         <v>669</v>
@@ -9123,10 +9123,10 @@
         <v>647</v>
       </c>
       <c r="C333" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D333" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E333" t="s">
         <v>671</v>
@@ -9143,10 +9143,10 @@
         <v>647</v>
       </c>
       <c r="C334" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D334" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E334" t="s">
         <v>673</v>
@@ -9166,7 +9166,7 @@
         <v>513</v>
       </c>
       <c r="D335" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E335" t="s">
         <v>675</v>
@@ -9183,10 +9183,10 @@
         <v>647</v>
       </c>
       <c r="C336" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D336" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E336" t="s">
         <v>677</v>
@@ -9203,13 +9203,13 @@
         <v>647</v>
       </c>
       <c r="C337" t="s">
+        <v>662</v>
+      </c>
+      <c r="D337" t="s">
+        <v>648</v>
+      </c>
+      <c r="E337" t="s">
         <v>679</v>
-      </c>
-      <c r="D337" t="s">
-        <v>649</v>
-      </c>
-      <c r="E337" t="s">
-        <v>680</v>
       </c>
       <c r="F337" s="1">
         <v>46245</v>
@@ -9217,19 +9217,19 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
+        <v>680</v>
+      </c>
+      <c r="B338" t="s">
+        <v>647</v>
+      </c>
+      <c r="C338" t="s">
         <v>681</v>
       </c>
-      <c r="B338" t="s">
+      <c r="D338" t="s">
+        <v>648</v>
+      </c>
+      <c r="E338" t="s">
         <v>682</v>
-      </c>
-      <c r="C338" t="s">
-        <v>683</v>
-      </c>
-      <c r="D338" t="s">
-        <v>649</v>
-      </c>
-      <c r="E338" t="s">
-        <v>684</v>
       </c>
       <c r="F338" s="1">
         <v>46245</v>
@@ -9237,16 +9237,16 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
+        <v>683</v>
+      </c>
+      <c r="B339" t="s">
+        <v>684</v>
+      </c>
+      <c r="C339" t="s">
         <v>685</v>
       </c>
-      <c r="B339" t="s">
-        <v>647</v>
-      </c>
-      <c r="C339" t="s">
-        <v>683</v>
-      </c>
       <c r="D339" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E339" t="s">
         <v>686</v>
@@ -9263,10 +9263,10 @@
         <v>647</v>
       </c>
       <c r="C340" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D340" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E340" t="s">
         <v>688</v>
@@ -9283,10 +9283,10 @@
         <v>647</v>
       </c>
       <c r="C341" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D341" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E341" t="s">
         <v>690</v>
@@ -9303,10 +9303,10 @@
         <v>647</v>
       </c>
       <c r="C342" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D342" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E342" t="s">
         <v>692</v>
@@ -9323,10 +9323,10 @@
         <v>647</v>
       </c>
       <c r="C343" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D343" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E343" t="s">
         <v>694</v>
@@ -9343,10 +9343,10 @@
         <v>647</v>
       </c>
       <c r="C344" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D344" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E344" t="s">
         <v>696</v>
@@ -9363,10 +9363,10 @@
         <v>647</v>
       </c>
       <c r="C345" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D345" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E345" t="s">
         <v>698</v>
@@ -9383,10 +9383,10 @@
         <v>647</v>
       </c>
       <c r="C346" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D346" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E346" t="s">
         <v>700</v>
@@ -9403,10 +9403,10 @@
         <v>647</v>
       </c>
       <c r="C347" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D347" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E347" t="s">
         <v>702</v>
@@ -9423,13 +9423,13 @@
         <v>647</v>
       </c>
       <c r="C348" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D348" t="s">
+        <v>648</v>
+      </c>
+      <c r="E348" t="s">
         <v>649</v>
-      </c>
-      <c r="E348" t="s">
-        <v>650</v>
       </c>
       <c r="F348" s="1">
         <v>46245</v>
@@ -9437,16 +9437,16 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
+        <v>650</v>
+      </c>
+      <c r="B349" t="s">
+        <v>647</v>
+      </c>
+      <c r="C349" t="s">
         <v>651</v>
       </c>
-      <c r="B349" t="s">
-        <v>647</v>
-      </c>
-      <c r="C349" t="s">
-        <v>648</v>
-      </c>
       <c r="D349" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E349" t="s">
         <v>652</v>
@@ -9463,10 +9463,10 @@
         <v>647</v>
       </c>
       <c r="C350" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D350" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E350" t="s">
         <v>654</v>
@@ -9483,10 +9483,10 @@
         <v>647</v>
       </c>
       <c r="C351" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D351" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E351" t="s">
         <v>656</v>
@@ -9503,10 +9503,10 @@
         <v>647</v>
       </c>
       <c r="C352" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D352" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E352" t="s">
         <v>658</v>
@@ -9523,13 +9523,13 @@
         <v>647</v>
       </c>
       <c r="C353" t="s">
+        <v>651</v>
+      </c>
+      <c r="D353" t="s">
+        <v>648</v>
+      </c>
+      <c r="E353" t="s">
         <v>660</v>
-      </c>
-      <c r="D353" t="s">
-        <v>649</v>
-      </c>
-      <c r="E353" t="s">
-        <v>661</v>
       </c>
       <c r="F353" s="1">
         <v>46245</v>
@@ -9537,16 +9537,16 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" t="s">
+        <v>661</v>
+      </c>
+      <c r="B354" t="s">
+        <v>647</v>
+      </c>
+      <c r="C354" t="s">
         <v>662</v>
       </c>
-      <c r="B354" t="s">
-        <v>647</v>
-      </c>
-      <c r="C354" t="s">
-        <v>383</v>
-      </c>
       <c r="D354" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E354" t="s">
         <v>663</v>
@@ -9563,10 +9563,10 @@
         <v>647</v>
       </c>
       <c r="C355" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D355" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E355" t="s">
         <v>665</v>
@@ -9583,10 +9583,10 @@
         <v>647</v>
       </c>
       <c r="C356" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D356" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E356" t="s">
         <v>667</v>
@@ -9603,10 +9603,10 @@
         <v>647</v>
       </c>
       <c r="C357" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D357" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E357" t="s">
         <v>669</v>
@@ -9623,10 +9623,10 @@
         <v>647</v>
       </c>
       <c r="C358" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D358" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E358" t="s">
         <v>671</v>
@@ -9643,10 +9643,10 @@
         <v>647</v>
       </c>
       <c r="C359" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D359" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E359" t="s">
         <v>673</v>
@@ -9666,7 +9666,7 @@
         <v>513</v>
       </c>
       <c r="D360" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E360" t="s">
         <v>675</v>
@@ -9683,10 +9683,10 @@
         <v>647</v>
       </c>
       <c r="C361" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D361" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E361" t="s">
         <v>677</v>
@@ -9703,13 +9703,13 @@
         <v>647</v>
       </c>
       <c r="C362" t="s">
+        <v>662</v>
+      </c>
+      <c r="D362" t="s">
+        <v>648</v>
+      </c>
+      <c r="E362" t="s">
         <v>679</v>
-      </c>
-      <c r="D362" t="s">
-        <v>649</v>
-      </c>
-      <c r="E362" t="s">
-        <v>680</v>
       </c>
       <c r="F362" s="1">
         <v>46245</v>
@@ -9717,19 +9717,19 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
+        <v>680</v>
+      </c>
+      <c r="B363" t="s">
+        <v>647</v>
+      </c>
+      <c r="C363" t="s">
         <v>681</v>
       </c>
-      <c r="B363" t="s">
+      <c r="D363" t="s">
+        <v>648</v>
+      </c>
+      <c r="E363" t="s">
         <v>682</v>
-      </c>
-      <c r="C363" t="s">
-        <v>683</v>
-      </c>
-      <c r="D363" t="s">
-        <v>649</v>
-      </c>
-      <c r="E363" t="s">
-        <v>684</v>
       </c>
       <c r="F363" s="1">
         <v>46245</v>
@@ -9737,16 +9737,16 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" t="s">
+        <v>683</v>
+      </c>
+      <c r="B364" t="s">
+        <v>684</v>
+      </c>
+      <c r="C364" t="s">
         <v>685</v>
       </c>
-      <c r="B364" t="s">
-        <v>647</v>
-      </c>
-      <c r="C364" t="s">
-        <v>683</v>
-      </c>
       <c r="D364" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E364" t="s">
         <v>686</v>
@@ -9763,10 +9763,10 @@
         <v>647</v>
       </c>
       <c r="C365" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D365" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E365" t="s">
         <v>688</v>
@@ -9783,10 +9783,10 @@
         <v>647</v>
       </c>
       <c r="C366" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D366" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E366" t="s">
         <v>690</v>
@@ -9803,10 +9803,10 @@
         <v>647</v>
       </c>
       <c r="C367" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D367" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E367" t="s">
         <v>692</v>
@@ -9823,10 +9823,10 @@
         <v>647</v>
       </c>
       <c r="C368" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D368" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E368" t="s">
         <v>694</v>
@@ -9843,10 +9843,10 @@
         <v>647</v>
       </c>
       <c r="C369" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D369" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E369" t="s">
         <v>696</v>
@@ -9863,10 +9863,10 @@
         <v>647</v>
       </c>
       <c r="C370" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D370" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E370" t="s">
         <v>698</v>
@@ -9883,10 +9883,10 @@
         <v>647</v>
       </c>
       <c r="C371" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D371" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E371" t="s">
         <v>700</v>
@@ -9903,10 +9903,10 @@
         <v>647</v>
       </c>
       <c r="C372" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D372" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E372" t="s">
         <v>702</v>
@@ -9923,13 +9923,13 @@
         <v>647</v>
       </c>
       <c r="C373" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D373" t="s">
+        <v>648</v>
+      </c>
+      <c r="E373" t="s">
         <v>649</v>
-      </c>
-      <c r="E373" t="s">
-        <v>650</v>
       </c>
       <c r="F373" s="1">
         <v>46245</v>
@@ -9937,16 +9937,16 @@
     </row>
     <row r="374" spans="1:6">
       <c r="A374" t="s">
+        <v>650</v>
+      </c>
+      <c r="B374" t="s">
+        <v>647</v>
+      </c>
+      <c r="C374" t="s">
         <v>651</v>
       </c>
-      <c r="B374" t="s">
-        <v>647</v>
-      </c>
-      <c r="C374" t="s">
-        <v>648</v>
-      </c>
       <c r="D374" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E374" t="s">
         <v>652</v>
@@ -9963,10 +9963,10 @@
         <v>647</v>
       </c>
       <c r="C375" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D375" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E375" t="s">
         <v>654</v>
@@ -9983,10 +9983,10 @@
         <v>647</v>
       </c>
       <c r="C376" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D376" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E376" t="s">
         <v>656</v>
@@ -10003,10 +10003,10 @@
         <v>647</v>
       </c>
       <c r="C377" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D377" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E377" t="s">
         <v>658</v>
@@ -10023,13 +10023,13 @@
         <v>647</v>
       </c>
       <c r="C378" t="s">
+        <v>651</v>
+      </c>
+      <c r="D378" t="s">
+        <v>648</v>
+      </c>
+      <c r="E378" t="s">
         <v>660</v>
-      </c>
-      <c r="D378" t="s">
-        <v>649</v>
-      </c>
-      <c r="E378" t="s">
-        <v>661</v>
       </c>
       <c r="F378" s="1">
         <v>46245</v>
@@ -10037,16 +10037,16 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" t="s">
+        <v>661</v>
+      </c>
+      <c r="B379" t="s">
+        <v>647</v>
+      </c>
+      <c r="C379" t="s">
         <v>662</v>
       </c>
-      <c r="B379" t="s">
-        <v>647</v>
-      </c>
-      <c r="C379" t="s">
-        <v>383</v>
-      </c>
       <c r="D379" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E379" t="s">
         <v>663</v>
@@ -10063,10 +10063,10 @@
         <v>647</v>
       </c>
       <c r="C380" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D380" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E380" t="s">
         <v>665</v>
@@ -10083,10 +10083,10 @@
         <v>647</v>
       </c>
       <c r="C381" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D381" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E381" t="s">
         <v>667</v>
@@ -10103,10 +10103,10 @@
         <v>647</v>
       </c>
       <c r="C382" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D382" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E382" t="s">
         <v>669</v>
@@ -10123,10 +10123,10 @@
         <v>647</v>
       </c>
       <c r="C383" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D383" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E383" t="s">
         <v>671</v>
@@ -10143,10 +10143,10 @@
         <v>647</v>
       </c>
       <c r="C384" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D384" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E384" t="s">
         <v>673</v>
@@ -10166,7 +10166,7 @@
         <v>513</v>
       </c>
       <c r="D385" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E385" t="s">
         <v>675</v>
@@ -10183,10 +10183,10 @@
         <v>647</v>
       </c>
       <c r="C386" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D386" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E386" t="s">
         <v>677</v>
@@ -10203,13 +10203,13 @@
         <v>647</v>
       </c>
       <c r="C387" t="s">
+        <v>662</v>
+      </c>
+      <c r="D387" t="s">
+        <v>648</v>
+      </c>
+      <c r="E387" t="s">
         <v>679</v>
-      </c>
-      <c r="D387" t="s">
-        <v>649</v>
-      </c>
-      <c r="E387" t="s">
-        <v>680</v>
       </c>
       <c r="F387" s="1">
         <v>46245</v>
@@ -10217,19 +10217,19 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
+        <v>680</v>
+      </c>
+      <c r="B388" t="s">
+        <v>647</v>
+      </c>
+      <c r="C388" t="s">
         <v>681</v>
       </c>
-      <c r="B388" t="s">
+      <c r="D388" t="s">
+        <v>648</v>
+      </c>
+      <c r="E388" t="s">
         <v>682</v>
-      </c>
-      <c r="C388" t="s">
-        <v>683</v>
-      </c>
-      <c r="D388" t="s">
-        <v>649</v>
-      </c>
-      <c r="E388" t="s">
-        <v>684</v>
       </c>
       <c r="F388" s="1">
         <v>46245</v>
@@ -10237,16 +10237,16 @@
     </row>
     <row r="389" spans="1:6">
       <c r="A389" t="s">
+        <v>683</v>
+      </c>
+      <c r="B389" t="s">
+        <v>684</v>
+      </c>
+      <c r="C389" t="s">
         <v>685</v>
       </c>
-      <c r="B389" t="s">
-        <v>647</v>
-      </c>
-      <c r="C389" t="s">
-        <v>683</v>
-      </c>
       <c r="D389" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E389" t="s">
         <v>686</v>
@@ -10263,10 +10263,10 @@
         <v>647</v>
       </c>
       <c r="C390" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D390" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E390" t="s">
         <v>688</v>
@@ -10283,10 +10283,10 @@
         <v>647</v>
       </c>
       <c r="C391" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D391" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E391" t="s">
         <v>690</v>
@@ -10303,10 +10303,10 @@
         <v>647</v>
       </c>
       <c r="C392" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D392" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E392" t="s">
         <v>692</v>
@@ -10323,10 +10323,10 @@
         <v>647</v>
       </c>
       <c r="C393" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D393" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E393" t="s">
         <v>694</v>
@@ -10343,10 +10343,10 @@
         <v>647</v>
       </c>
       <c r="C394" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D394" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E394" t="s">
         <v>696</v>
@@ -10363,10 +10363,10 @@
         <v>647</v>
       </c>
       <c r="C395" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D395" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E395" t="s">
         <v>698</v>
@@ -10383,10 +10383,10 @@
         <v>647</v>
       </c>
       <c r="C396" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D396" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E396" t="s">
         <v>700</v>
@@ -10403,10 +10403,10 @@
         <v>647</v>
       </c>
       <c r="C397" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D397" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E397" t="s">
         <v>702</v>
@@ -10423,13 +10423,13 @@
         <v>647</v>
       </c>
       <c r="C398" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D398" t="s">
+        <v>648</v>
+      </c>
+      <c r="E398" t="s">
         <v>649</v>
-      </c>
-      <c r="E398" t="s">
-        <v>650</v>
       </c>
       <c r="F398" s="1">
         <v>46245</v>
@@ -10437,16 +10437,16 @@
     </row>
     <row r="399" spans="1:6">
       <c r="A399" t="s">
+        <v>650</v>
+      </c>
+      <c r="B399" t="s">
+        <v>647</v>
+      </c>
+      <c r="C399" t="s">
         <v>651</v>
       </c>
-      <c r="B399" t="s">
-        <v>647</v>
-      </c>
-      <c r="C399" t="s">
-        <v>648</v>
-      </c>
       <c r="D399" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E399" t="s">
         <v>652</v>
@@ -10463,10 +10463,10 @@
         <v>647</v>
       </c>
       <c r="C400" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D400" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E400" t="s">
         <v>654</v>
@@ -10483,10 +10483,10 @@
         <v>647</v>
       </c>
       <c r="C401" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D401" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E401" t="s">
         <v>656</v>
@@ -10503,10 +10503,10 @@
         <v>647</v>
       </c>
       <c r="C402" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D402" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E402" t="s">
         <v>658</v>
@@ -10523,13 +10523,13 @@
         <v>647</v>
       </c>
       <c r="C403" t="s">
+        <v>651</v>
+      </c>
+      <c r="D403" t="s">
+        <v>648</v>
+      </c>
+      <c r="E403" t="s">
         <v>660</v>
-      </c>
-      <c r="D403" t="s">
-        <v>649</v>
-      </c>
-      <c r="E403" t="s">
-        <v>661</v>
       </c>
       <c r="F403" s="1">
         <v>46245</v>
@@ -10537,16 +10537,16 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" t="s">
+        <v>661</v>
+      </c>
+      <c r="B404" t="s">
+        <v>647</v>
+      </c>
+      <c r="C404" t="s">
         <v>662</v>
       </c>
-      <c r="B404" t="s">
-        <v>647</v>
-      </c>
-      <c r="C404" t="s">
-        <v>383</v>
-      </c>
       <c r="D404" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E404" t="s">
         <v>663</v>
@@ -10563,10 +10563,10 @@
         <v>647</v>
       </c>
       <c r="C405" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D405" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E405" t="s">
         <v>665</v>
@@ -10583,10 +10583,10 @@
         <v>647</v>
       </c>
       <c r="C406" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D406" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E406" t="s">
         <v>667</v>
@@ -10603,10 +10603,10 @@
         <v>647</v>
       </c>
       <c r="C407" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D407" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E407" t="s">
         <v>669</v>
@@ -10623,10 +10623,10 @@
         <v>647</v>
       </c>
       <c r="C408" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D408" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E408" t="s">
         <v>671</v>
@@ -10643,10 +10643,10 @@
         <v>647</v>
       </c>
       <c r="C409" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D409" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E409" t="s">
         <v>673</v>
@@ -10666,7 +10666,7 @@
         <v>513</v>
       </c>
       <c r="D410" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E410" t="s">
         <v>675</v>
@@ -10683,10 +10683,10 @@
         <v>647</v>
       </c>
       <c r="C411" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D411" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E411" t="s">
         <v>677</v>
@@ -10703,13 +10703,13 @@
         <v>647</v>
       </c>
       <c r="C412" t="s">
+        <v>662</v>
+      </c>
+      <c r="D412" t="s">
+        <v>648</v>
+      </c>
+      <c r="E412" t="s">
         <v>679</v>
-      </c>
-      <c r="D412" t="s">
-        <v>649</v>
-      </c>
-      <c r="E412" t="s">
-        <v>680</v>
       </c>
       <c r="F412" s="1">
         <v>46245</v>
@@ -10717,19 +10717,19 @@
     </row>
     <row r="413" spans="1:6">
       <c r="A413" t="s">
+        <v>680</v>
+      </c>
+      <c r="B413" t="s">
+        <v>647</v>
+      </c>
+      <c r="C413" t="s">
         <v>681</v>
       </c>
-      <c r="B413" t="s">
+      <c r="D413" t="s">
+        <v>648</v>
+      </c>
+      <c r="E413" t="s">
         <v>682</v>
-      </c>
-      <c r="C413" t="s">
-        <v>683</v>
-      </c>
-      <c r="D413" t="s">
-        <v>649</v>
-      </c>
-      <c r="E413" t="s">
-        <v>684</v>
       </c>
       <c r="F413" s="1">
         <v>46245</v>
@@ -10737,16 +10737,16 @@
     </row>
     <row r="414" spans="1:6">
       <c r="A414" t="s">
+        <v>683</v>
+      </c>
+      <c r="B414" t="s">
+        <v>684</v>
+      </c>
+      <c r="C414" t="s">
         <v>685</v>
       </c>
-      <c r="B414" t="s">
-        <v>647</v>
-      </c>
-      <c r="C414" t="s">
-        <v>683</v>
-      </c>
       <c r="D414" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E414" t="s">
         <v>686</v>
@@ -10763,10 +10763,10 @@
         <v>647</v>
       </c>
       <c r="C415" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D415" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E415" t="s">
         <v>688</v>
@@ -10783,10 +10783,10 @@
         <v>647</v>
       </c>
       <c r="C416" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D416" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E416" t="s">
         <v>690</v>
@@ -10803,10 +10803,10 @@
         <v>647</v>
       </c>
       <c r="C417" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D417" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E417" t="s">
         <v>692</v>
@@ -10823,10 +10823,10 @@
         <v>647</v>
       </c>
       <c r="C418" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D418" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E418" t="s">
         <v>694</v>
@@ -10843,10 +10843,10 @@
         <v>647</v>
       </c>
       <c r="C419" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D419" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E419" t="s">
         <v>696</v>
@@ -10863,10 +10863,10 @@
         <v>647</v>
       </c>
       <c r="C420" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D420" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E420" t="s">
         <v>698</v>
@@ -10883,10 +10883,10 @@
         <v>647</v>
       </c>
       <c r="C421" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D421" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E421" t="s">
         <v>700</v>
@@ -10903,10 +10903,10 @@
         <v>647</v>
       </c>
       <c r="C422" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D422" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E422" t="s">
         <v>702</v>
@@ -10923,13 +10923,13 @@
         <v>647</v>
       </c>
       <c r="C423" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D423" t="s">
+        <v>648</v>
+      </c>
+      <c r="E423" t="s">
         <v>649</v>
-      </c>
-      <c r="E423" t="s">
-        <v>650</v>
       </c>
       <c r="F423" s="1">
         <v>46245</v>
@@ -10937,16 +10937,16 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" t="s">
+        <v>650</v>
+      </c>
+      <c r="B424" t="s">
+        <v>647</v>
+      </c>
+      <c r="C424" t="s">
         <v>651</v>
       </c>
-      <c r="B424" t="s">
-        <v>647</v>
-      </c>
-      <c r="C424" t="s">
-        <v>648</v>
-      </c>
       <c r="D424" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E424" t="s">
         <v>652</v>
@@ -10963,10 +10963,10 @@
         <v>647</v>
       </c>
       <c r="C425" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D425" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E425" t="s">
         <v>654</v>
@@ -10983,10 +10983,10 @@
         <v>647</v>
       </c>
       <c r="C426" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D426" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E426" t="s">
         <v>656</v>
@@ -11003,10 +11003,10 @@
         <v>647</v>
       </c>
       <c r="C427" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D427" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E427" t="s">
         <v>658</v>
@@ -11023,13 +11023,13 @@
         <v>647</v>
       </c>
       <c r="C428" t="s">
+        <v>651</v>
+      </c>
+      <c r="D428" t="s">
+        <v>648</v>
+      </c>
+      <c r="E428" t="s">
         <v>660</v>
-      </c>
-      <c r="D428" t="s">
-        <v>649</v>
-      </c>
-      <c r="E428" t="s">
-        <v>661</v>
       </c>
       <c r="F428" s="1">
         <v>46245</v>
@@ -11037,16 +11037,16 @@
     </row>
     <row r="429" spans="1:6">
       <c r="A429" t="s">
+        <v>661</v>
+      </c>
+      <c r="B429" t="s">
+        <v>647</v>
+      </c>
+      <c r="C429" t="s">
         <v>662</v>
       </c>
-      <c r="B429" t="s">
-        <v>647</v>
-      </c>
-      <c r="C429" t="s">
-        <v>383</v>
-      </c>
       <c r="D429" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E429" t="s">
         <v>663</v>
@@ -11063,10 +11063,10 @@
         <v>647</v>
       </c>
       <c r="C430" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D430" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E430" t="s">
         <v>665</v>
@@ -11083,10 +11083,10 @@
         <v>647</v>
       </c>
       <c r="C431" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D431" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E431" t="s">
         <v>667</v>
@@ -11103,10 +11103,10 @@
         <v>647</v>
       </c>
       <c r="C432" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D432" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E432" t="s">
         <v>669</v>
@@ -11123,10 +11123,10 @@
         <v>647</v>
       </c>
       <c r="C433" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D433" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E433" t="s">
         <v>671</v>
@@ -11143,10 +11143,10 @@
         <v>647</v>
       </c>
       <c r="C434" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D434" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E434" t="s">
         <v>673</v>
@@ -11166,7 +11166,7 @@
         <v>513</v>
       </c>
       <c r="D435" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E435" t="s">
         <v>675</v>
@@ -11183,10 +11183,10 @@
         <v>647</v>
       </c>
       <c r="C436" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D436" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E436" t="s">
         <v>677</v>
@@ -11203,13 +11203,13 @@
         <v>647</v>
       </c>
       <c r="C437" t="s">
+        <v>662</v>
+      </c>
+      <c r="D437" t="s">
+        <v>648</v>
+      </c>
+      <c r="E437" t="s">
         <v>679</v>
-      </c>
-      <c r="D437" t="s">
-        <v>649</v>
-      </c>
-      <c r="E437" t="s">
-        <v>680</v>
       </c>
       <c r="F437" s="1">
         <v>46245</v>
@@ -11217,19 +11217,19 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
+        <v>680</v>
+      </c>
+      <c r="B438" t="s">
+        <v>647</v>
+      </c>
+      <c r="C438" t="s">
         <v>681</v>
       </c>
-      <c r="B438" t="s">
+      <c r="D438" t="s">
+        <v>648</v>
+      </c>
+      <c r="E438" t="s">
         <v>682</v>
-      </c>
-      <c r="C438" t="s">
-        <v>683</v>
-      </c>
-      <c r="D438" t="s">
-        <v>649</v>
-      </c>
-      <c r="E438" t="s">
-        <v>684</v>
       </c>
       <c r="F438" s="1">
         <v>46245</v>
@@ -11237,16 +11237,16 @@
     </row>
     <row r="439" spans="1:6">
       <c r="A439" t="s">
+        <v>683</v>
+      </c>
+      <c r="B439" t="s">
+        <v>684</v>
+      </c>
+      <c r="C439" t="s">
         <v>685</v>
       </c>
-      <c r="B439" t="s">
-        <v>647</v>
-      </c>
-      <c r="C439" t="s">
-        <v>683</v>
-      </c>
       <c r="D439" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E439" t="s">
         <v>686</v>
@@ -11263,10 +11263,10 @@
         <v>647</v>
       </c>
       <c r="C440" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D440" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E440" t="s">
         <v>688</v>
@@ -11283,10 +11283,10 @@
         <v>647</v>
       </c>
       <c r="C441" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D441" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E441" t="s">
         <v>690</v>
@@ -11303,10 +11303,10 @@
         <v>647</v>
       </c>
       <c r="C442" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D442" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E442" t="s">
         <v>692</v>
@@ -11323,10 +11323,10 @@
         <v>647</v>
       </c>
       <c r="C443" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D443" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E443" t="s">
         <v>694</v>
@@ -11343,10 +11343,10 @@
         <v>647</v>
       </c>
       <c r="C444" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D444" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E444" t="s">
         <v>696</v>
@@ -11363,10 +11363,10 @@
         <v>647</v>
       </c>
       <c r="C445" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D445" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E445" t="s">
         <v>698</v>
@@ -11383,10 +11383,10 @@
         <v>647</v>
       </c>
       <c r="C446" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D446" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E446" t="s">
         <v>700</v>
@@ -11403,10 +11403,10 @@
         <v>647</v>
       </c>
       <c r="C447" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D447" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E447" t="s">
         <v>702</v>
@@ -11423,13 +11423,13 @@
         <v>647</v>
       </c>
       <c r="C448" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D448" t="s">
+        <v>648</v>
+      </c>
+      <c r="E448" t="s">
         <v>649</v>
-      </c>
-      <c r="E448" t="s">
-        <v>650</v>
       </c>
       <c r="F448" s="1">
         <v>46245</v>
@@ -11437,16 +11437,16 @@
     </row>
     <row r="449" spans="1:6">
       <c r="A449" t="s">
+        <v>650</v>
+      </c>
+      <c r="B449" t="s">
+        <v>647</v>
+      </c>
+      <c r="C449" t="s">
         <v>651</v>
       </c>
-      <c r="B449" t="s">
-        <v>647</v>
-      </c>
-      <c r="C449" t="s">
-        <v>648</v>
-      </c>
       <c r="D449" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E449" t="s">
         <v>652</v>
@@ -11463,10 +11463,10 @@
         <v>647</v>
       </c>
       <c r="C450" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D450" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E450" t="s">
         <v>654</v>
@@ -11483,10 +11483,10 @@
         <v>647</v>
       </c>
       <c r="C451" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D451" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E451" t="s">
         <v>656</v>
@@ -11503,10 +11503,10 @@
         <v>647</v>
       </c>
       <c r="C452" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D452" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E452" t="s">
         <v>658</v>
@@ -11523,13 +11523,13 @@
         <v>647</v>
       </c>
       <c r="C453" t="s">
+        <v>651</v>
+      </c>
+      <c r="D453" t="s">
+        <v>648</v>
+      </c>
+      <c r="E453" t="s">
         <v>660</v>
-      </c>
-      <c r="D453" t="s">
-        <v>649</v>
-      </c>
-      <c r="E453" t="s">
-        <v>661</v>
       </c>
       <c r="F453" s="1">
         <v>46245</v>
@@ -11537,16 +11537,16 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
+        <v>661</v>
+      </c>
+      <c r="B454" t="s">
+        <v>647</v>
+      </c>
+      <c r="C454" t="s">
         <v>662</v>
       </c>
-      <c r="B454" t="s">
-        <v>647</v>
-      </c>
-      <c r="C454" t="s">
-        <v>383</v>
-      </c>
       <c r="D454" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E454" t="s">
         <v>663</v>
@@ -11563,10 +11563,10 @@
         <v>647</v>
       </c>
       <c r="C455" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D455" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E455" t="s">
         <v>665</v>
@@ -11583,10 +11583,10 @@
         <v>647</v>
       </c>
       <c r="C456" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D456" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E456" t="s">
         <v>667</v>
@@ -11603,10 +11603,10 @@
         <v>647</v>
       </c>
       <c r="C457" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D457" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E457" t="s">
         <v>669</v>
@@ -11623,10 +11623,10 @@
         <v>647</v>
       </c>
       <c r="C458" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D458" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E458" t="s">
         <v>671</v>
@@ -11643,10 +11643,10 @@
         <v>647</v>
       </c>
       <c r="C459" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D459" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E459" t="s">
         <v>673</v>
@@ -11666,7 +11666,7 @@
         <v>513</v>
       </c>
       <c r="D460" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E460" t="s">
         <v>675</v>
@@ -11683,10 +11683,10 @@
         <v>647</v>
       </c>
       <c r="C461" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D461" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E461" t="s">
         <v>677</v>
@@ -11703,13 +11703,13 @@
         <v>647</v>
       </c>
       <c r="C462" t="s">
+        <v>662</v>
+      </c>
+      <c r="D462" t="s">
+        <v>648</v>
+      </c>
+      <c r="E462" t="s">
         <v>679</v>
-      </c>
-      <c r="D462" t="s">
-        <v>649</v>
-      </c>
-      <c r="E462" t="s">
-        <v>680</v>
       </c>
       <c r="F462" s="1">
         <v>46245</v>
@@ -11717,19 +11717,19 @@
     </row>
     <row r="463" spans="1:6">
       <c r="A463" t="s">
+        <v>680</v>
+      </c>
+      <c r="B463" t="s">
+        <v>647</v>
+      </c>
+      <c r="C463" t="s">
         <v>681</v>
       </c>
-      <c r="B463" t="s">
+      <c r="D463" t="s">
+        <v>648</v>
+      </c>
+      <c r="E463" t="s">
         <v>682</v>
-      </c>
-      <c r="C463" t="s">
-        <v>683</v>
-      </c>
-      <c r="D463" t="s">
-        <v>649</v>
-      </c>
-      <c r="E463" t="s">
-        <v>684</v>
       </c>
       <c r="F463" s="1">
         <v>46245</v>
@@ -11737,16 +11737,16 @@
     </row>
     <row r="464" spans="1:6">
       <c r="A464" t="s">
+        <v>683</v>
+      </c>
+      <c r="B464" t="s">
+        <v>684</v>
+      </c>
+      <c r="C464" t="s">
         <v>685</v>
       </c>
-      <c r="B464" t="s">
-        <v>647</v>
-      </c>
-      <c r="C464" t="s">
-        <v>683</v>
-      </c>
       <c r="D464" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E464" t="s">
         <v>686</v>
@@ -11763,10 +11763,10 @@
         <v>647</v>
       </c>
       <c r="C465" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D465" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E465" t="s">
         <v>688</v>
@@ -11783,10 +11783,10 @@
         <v>647</v>
       </c>
       <c r="C466" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D466" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E466" t="s">
         <v>690</v>
@@ -11803,10 +11803,10 @@
         <v>647</v>
       </c>
       <c r="C467" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D467" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E467" t="s">
         <v>692</v>
@@ -11823,10 +11823,10 @@
         <v>647</v>
       </c>
       <c r="C468" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D468" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E468" t="s">
         <v>694</v>
@@ -11843,10 +11843,10 @@
         <v>647</v>
       </c>
       <c r="C469" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D469" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E469" t="s">
         <v>696</v>
@@ -11863,10 +11863,10 @@
         <v>647</v>
       </c>
       <c r="C470" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D470" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E470" t="s">
         <v>698</v>
@@ -11883,10 +11883,10 @@
         <v>647</v>
       </c>
       <c r="C471" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D471" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E471" t="s">
         <v>700</v>
@@ -11903,10 +11903,10 @@
         <v>647</v>
       </c>
       <c r="C472" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D472" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E472" t="s">
         <v>702</v>
@@ -11923,13 +11923,13 @@
         <v>647</v>
       </c>
       <c r="C473" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D473" t="s">
+        <v>648</v>
+      </c>
+      <c r="E473" t="s">
         <v>649</v>
-      </c>
-      <c r="E473" t="s">
-        <v>650</v>
       </c>
       <c r="F473" s="1">
         <v>46245</v>
@@ -11937,16 +11937,16 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" t="s">
+        <v>650</v>
+      </c>
+      <c r="B474" t="s">
+        <v>647</v>
+      </c>
+      <c r="C474" t="s">
         <v>651</v>
       </c>
-      <c r="B474" t="s">
-        <v>647</v>
-      </c>
-      <c r="C474" t="s">
-        <v>648</v>
-      </c>
       <c r="D474" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E474" t="s">
         <v>652</v>
@@ -11963,10 +11963,10 @@
         <v>647</v>
       </c>
       <c r="C475" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D475" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E475" t="s">
         <v>654</v>
@@ -11983,10 +11983,10 @@
         <v>647</v>
       </c>
       <c r="C476" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D476" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E476" t="s">
         <v>656</v>
@@ -12003,10 +12003,10 @@
         <v>647</v>
       </c>
       <c r="C477" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D477" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E477" t="s">
         <v>658</v>
@@ -12023,13 +12023,13 @@
         <v>647</v>
       </c>
       <c r="C478" t="s">
+        <v>651</v>
+      </c>
+      <c r="D478" t="s">
+        <v>648</v>
+      </c>
+      <c r="E478" t="s">
         <v>660</v>
-      </c>
-      <c r="D478" t="s">
-        <v>649</v>
-      </c>
-      <c r="E478" t="s">
-        <v>661</v>
       </c>
       <c r="F478" s="1">
         <v>46245</v>
@@ -12037,16 +12037,16 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" t="s">
+        <v>661</v>
+      </c>
+      <c r="B479" t="s">
+        <v>647</v>
+      </c>
+      <c r="C479" t="s">
         <v>662</v>
       </c>
-      <c r="B479" t="s">
-        <v>647</v>
-      </c>
-      <c r="C479" t="s">
-        <v>383</v>
-      </c>
       <c r="D479" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E479" t="s">
         <v>663</v>
@@ -12063,10 +12063,10 @@
         <v>647</v>
       </c>
       <c r="C480" t="s">
-        <v>513</v>
+        <v>383</v>
       </c>
       <c r="D480" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E480" t="s">
         <v>665</v>
@@ -12083,10 +12083,10 @@
         <v>647</v>
       </c>
       <c r="C481" t="s">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="D481" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E481" t="s">
         <v>667</v>
@@ -12103,10 +12103,10 @@
         <v>647</v>
       </c>
       <c r="C482" t="s">
-        <v>660</v>
+        <v>228</v>
       </c>
       <c r="D482" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E482" t="s">
         <v>669</v>
@@ -12123,10 +12123,10 @@
         <v>647</v>
       </c>
       <c r="C483" t="s">
-        <v>231</v>
+        <v>662</v>
       </c>
       <c r="D483" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E483" t="s">
         <v>671</v>
@@ -12143,10 +12143,10 @@
         <v>647</v>
       </c>
       <c r="C484" t="s">
-        <v>513</v>
+        <v>228</v>
       </c>
       <c r="D484" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E484" t="s">
         <v>673</v>
@@ -12166,7 +12166,7 @@
         <v>513</v>
       </c>
       <c r="D485" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E485" t="s">
         <v>675</v>
@@ -12183,10 +12183,10 @@
         <v>647</v>
       </c>
       <c r="C486" t="s">
-        <v>660</v>
+        <v>513</v>
       </c>
       <c r="D486" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E486" t="s">
         <v>677</v>
@@ -12203,13 +12203,13 @@
         <v>647</v>
       </c>
       <c r="C487" t="s">
+        <v>662</v>
+      </c>
+      <c r="D487" t="s">
+        <v>648</v>
+      </c>
+      <c r="E487" t="s">
         <v>679</v>
-      </c>
-      <c r="D487" t="s">
-        <v>649</v>
-      </c>
-      <c r="E487" t="s">
-        <v>680</v>
       </c>
       <c r="F487" s="1">
         <v>46245</v>
@@ -12217,19 +12217,19 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" t="s">
+        <v>680</v>
+      </c>
+      <c r="B488" t="s">
+        <v>647</v>
+      </c>
+      <c r="C488" t="s">
         <v>681</v>
       </c>
-      <c r="B488" t="s">
+      <c r="D488" t="s">
+        <v>648</v>
+      </c>
+      <c r="E488" t="s">
         <v>682</v>
-      </c>
-      <c r="C488" t="s">
-        <v>683</v>
-      </c>
-      <c r="D488" t="s">
-        <v>649</v>
-      </c>
-      <c r="E488" t="s">
-        <v>684</v>
       </c>
       <c r="F488" s="1">
         <v>46245</v>
@@ -12237,16 +12237,16 @@
     </row>
     <row r="489" spans="1:6">
       <c r="A489" t="s">
+        <v>683</v>
+      </c>
+      <c r="B489" t="s">
+        <v>684</v>
+      </c>
+      <c r="C489" t="s">
         <v>685</v>
       </c>
-      <c r="B489" t="s">
-        <v>647</v>
-      </c>
-      <c r="C489" t="s">
-        <v>683</v>
-      </c>
       <c r="D489" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E489" t="s">
         <v>686</v>
@@ -12263,10 +12263,10 @@
         <v>647</v>
       </c>
       <c r="C490" t="s">
-        <v>346</v>
+        <v>685</v>
       </c>
       <c r="D490" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E490" t="s">
         <v>688</v>
@@ -12283,10 +12283,10 @@
         <v>647</v>
       </c>
       <c r="C491" t="s">
-        <v>679</v>
+        <v>349</v>
       </c>
       <c r="D491" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E491" t="s">
         <v>690</v>
@@ -12303,10 +12303,10 @@
         <v>647</v>
       </c>
       <c r="C492" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="D492" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E492" t="s">
         <v>692</v>
@@ -12323,10 +12323,10 @@
         <v>647</v>
       </c>
       <c r="C493" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D493" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E493" t="s">
         <v>694</v>
@@ -12343,10 +12343,10 @@
         <v>647</v>
       </c>
       <c r="C494" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D494" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E494" t="s">
         <v>696</v>
@@ -12363,10 +12363,10 @@
         <v>647</v>
       </c>
       <c r="C495" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D495" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E495" t="s">
         <v>698</v>
@@ -12383,10 +12383,10 @@
         <v>647</v>
       </c>
       <c r="C496" t="s">
-        <v>403</v>
+        <v>349</v>
       </c>
       <c r="D496" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E496" t="s">
         <v>700</v>
@@ -12403,10 +12403,10 @@
         <v>647</v>
       </c>
       <c r="C497" t="s">
-        <v>683</v>
+        <v>403</v>
       </c>
       <c r="D497" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E497" t="s">
         <v>702</v>
